--- a/库存看板数据-模板.xlsx
+++ b/库存看板数据-模板.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FBA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销量" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库龄" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进销存报表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营-月重点数据总览" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="滤清备货逻辑表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VC库存" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库存明细报表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -42,7 +48,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,8 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -426,104 +433,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>商品编码</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>VC近30天</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PO在库</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>库龄超90天PO</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>PO库销比</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PO在途_VC</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SC近30天</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>海外仓在库</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>海外仓库销比</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>海外仓在途</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>VC-PO近30天</t>
+          <t>库存看板数据模板 · 使用说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>KX1EAF13900</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H2" t="n">
-        <v>200</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>60</v>
-      </c>
-      <c r="K2" t="n">
-        <v>30</v>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>本模板共5个子表，对应系统下载的5个表格，表头已与真实下载表完全一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>使用方式：把系统下载表格的【表头行删除】后，整表数据直接粘贴到对应子表（数据从第2行开始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>不需要填的子表可以留空：留空的数据看板自动用 BI/ERP 实时数据；填了的数据以你填的为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>五个子表：进销存报表（库存+销量+运营）、运营-月重点数据总览（运营月度利润/流量）、滤清备货逻辑表（SKU/ASIN/映射/备货）、VC库存（PO/VC渠道）、库存明细报表（BI仓库明细，含头程/采购在途）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>粘贴后保存文件，在看板「导入数据（总表）」选择此文件上传</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>常见问题</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Q: 粘贴后表头还在怎么办</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A: 上传时会自动识别表头行并跳过，不影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Q: 我的文件列顺序不完全一致</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A: 按列名识别，列顺序可以不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q: 只填了1个子表可以吗</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A: 可以，其余自动用实时数据</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -537,40 +570,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:AS1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>平台SKU</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>可用库存</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>头程在途</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1341EAF139XUS</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>300</v>
-      </c>
-      <c r="C2" t="n">
-        <v>80</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>品线</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>业务分类</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>运营</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>商品等级</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>开发人员</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用库存</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途库存</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用库存</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途库存</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>本地仓可用库存</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>总库存</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途库存</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>含采购在途总库存</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>总库存金额</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>含采购在途总库存金额</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>7天销量</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>14天销量</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>30天销量</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>30-60天销量</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>60-90天销量</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>近7天入库数量</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>近14天入库数量</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>近30天入库数量</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>采购单价</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>30天出库金额</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>成品库销比</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>离岸库销比</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>FBA库销比</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在库库销比</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途库销比</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>库销比-预警值</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>滞销数量</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>库销比-红线值</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>滞销金额</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>FBA30天销量</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>FBM30天销量</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>FBA首次到货时间</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>FBM首次到货时间</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>是否滞销</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>PO在库</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -584,32 +811,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>平台销售编码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>出库销量</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B0BR6M1KYF</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1476</v>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>出库销售额</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>推广占比</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>促销折扣占比</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>毛利润-实际</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>流量</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>店铺费用占比</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>头程占比</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>尾程占比</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>仓储占比</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -623,66 +902,1516 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:ID1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>产品编码</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>VIO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>大厂号</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>包装数量</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>商品状态</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>产品等级</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>历史运营</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>最新运营</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>商品状态是否淘汰</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>2月毛利率</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>2月VC毛利率</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>2月SC毛利率</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>12月-2月毛利率</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>12月-2月VC毛利率</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>12月-2月SC毛利率</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>5月-7月 毛利率</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>8-11毛利率</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>近30天毛利额</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>近30天毛利率</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>12月-2月均销量</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>2025年7月-9月均销量</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>2025年10月-11月月均销量</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（月均取值近30天销量）</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>全链路固定库销比</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量计入(加权月均）</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>1.2系数月销</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>历史Max月销</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>运营预估目标月销</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>加权月销</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>销量定级(AO列月销）</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>库销比 （月均销量取值AL列）</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>毛利率系数</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量 1219</t>
+        </is>
+      </c>
+      <c r="AU1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 1219</t>
+        </is>
+      </c>
+      <c r="AV1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="AW1" s="2" t="inlineStr">
+        <is>
+          <t>给供应商预测需求</t>
+        </is>
+      </c>
+      <c r="AX1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="AY1" s="2" t="inlineStr">
+        <is>
+          <t>加权月均</t>
+        </is>
+      </c>
+      <c r="AZ1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="BA1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="BB1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="BC1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="BF1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="BG1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="BH1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="BI1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量 0105</t>
+        </is>
+      </c>
+      <c r="BK1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0105</t>
+        </is>
+      </c>
+      <c r="BL1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="BM1" s="2" t="inlineStr">
+        <is>
+          <t>加权月均</t>
+        </is>
+      </c>
+      <c r="BN1" s="2" t="inlineStr">
+        <is>
+          <t>1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="BO1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="BP1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="BQ1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="BR1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="BS1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="BT1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="BU1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="BV1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="BW1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="BX1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="BY1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="BZ1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量 0120</t>
+        </is>
+      </c>
+      <c r="CA1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0120</t>
+        </is>
+      </c>
+      <c r="CB1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回01/23</t>
+        </is>
+      </c>
+      <c r="CC1" s="2" t="inlineStr">
+        <is>
+          <t>给供应商预需求-计划返回01/23</t>
+        </is>
+      </c>
+      <c r="CD1" s="2" t="inlineStr">
+        <is>
+          <t>商品等级</t>
+        </is>
+      </c>
+      <c r="CE1" s="2" t="inlineStr">
+        <is>
+          <t>装箱数</t>
+        </is>
+      </c>
+      <c r="CF1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="CG1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="CH1" s="2" t="inlineStr">
+        <is>
+          <t>加权月均</t>
+        </is>
+      </c>
+      <c r="CI1" s="2" t="inlineStr">
+        <is>
+          <t>1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="CJ1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="CK1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="CL1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="CM1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="CN1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="CO1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="CP1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="CQ1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="CR1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="CS1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="CT1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="CU1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量0302</t>
+        </is>
+      </c>
+      <c r="CV1" s="2" t="inlineStr">
+        <is>
+          <t>供应商预需求剩余数量</t>
+        </is>
+      </c>
+      <c r="CW1" s="2" t="inlineStr">
+        <is>
+          <t>最终需备货数量 0302</t>
+        </is>
+      </c>
+      <c r="CX1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0303</t>
+        </is>
+      </c>
+      <c r="CY1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回</t>
+        </is>
+      </c>
+      <c r="CZ1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="DA1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="DB1" s="2" t="inlineStr">
+        <is>
+          <t>加权月均</t>
+        </is>
+      </c>
+      <c r="DC1" s="2" t="inlineStr">
+        <is>
+          <t>1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="DD1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="DE1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="DF1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="DG1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="DH1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="DI1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="DJ1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="DK1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="DL1" s="2" t="inlineStr">
+        <is>
+          <t>金蝶云</t>
+        </is>
+      </c>
+      <c r="DM1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="DN1" s="2" t="inlineStr">
+        <is>
+          <t>全链路固定库销</t>
+        </is>
+      </c>
+      <c r="DO1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="DP1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="DQ1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量0311</t>
+        </is>
+      </c>
+      <c r="DR1" s="2" t="inlineStr">
+        <is>
+          <t>供应商预需求剩余数量</t>
+        </is>
+      </c>
+      <c r="DS1" s="2" t="inlineStr">
+        <is>
+          <t>最终需备货数量 0311</t>
+        </is>
+      </c>
+      <c r="DT1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0311</t>
+        </is>
+      </c>
+      <c r="DU1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回</t>
+        </is>
+      </c>
+      <c r="DV1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="DW1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="DX1" s="2" t="inlineStr">
+        <is>
+          <t>加权月均</t>
+        </is>
+      </c>
+      <c r="DY1" s="2" t="inlineStr">
+        <is>
+          <t>1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="DZ1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="EA1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="EB1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="EC1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="ED1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="EE1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="EF1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="EG1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="EH1" s="2" t="inlineStr">
+        <is>
+          <t>金蝶云</t>
+        </is>
+      </c>
+      <c r="EI1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="EJ1" s="2" t="inlineStr">
+        <is>
+          <t>全链路固定库销</t>
+        </is>
+      </c>
+      <c r="EK1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="EL1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="EM1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量0323</t>
+        </is>
+      </c>
+      <c r="EN1" s="2" t="inlineStr">
+        <is>
+          <t>供应商预需求剩余数量</t>
+        </is>
+      </c>
+      <c r="EO1" s="2" t="inlineStr">
+        <is>
+          <t>最终需备货数量 0323</t>
+        </is>
+      </c>
+      <c r="EP1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0323</t>
+        </is>
+      </c>
+      <c r="EQ1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回</t>
+        </is>
+      </c>
+      <c r="ER1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="ES1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="ET1" s="2" t="inlineStr">
+        <is>
+          <t>加权月均</t>
+        </is>
+      </c>
+      <c r="EU1" s="2" t="inlineStr">
+        <is>
+          <t>1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="EV1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="EW1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="EX1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="EY1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="EZ1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="FA1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="FB1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="FC1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="FD1" s="2" t="inlineStr">
+        <is>
+          <t>金蝶云</t>
+        </is>
+      </c>
+      <c r="FE1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="FF1" s="2" t="inlineStr">
+        <is>
+          <t>全链路固定库销</t>
+        </is>
+      </c>
+      <c r="FG1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="FH1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="FI1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量0401</t>
+        </is>
+      </c>
+      <c r="FJ1" s="2" t="inlineStr">
+        <is>
+          <t>供应商预需求剩余数量</t>
+        </is>
+      </c>
+      <c r="FK1" s="2" t="inlineStr">
+        <is>
+          <t>最终需备货数量 0401</t>
+        </is>
+      </c>
+      <c r="FL1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0401</t>
+        </is>
+      </c>
+      <c r="FM1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回</t>
+        </is>
+      </c>
+      <c r="FN1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="FO1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="FP1" s="2" t="inlineStr">
+        <is>
+          <t>加权月均</t>
+        </is>
+      </c>
+      <c r="FQ1" s="2" t="inlineStr">
+        <is>
+          <t>1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="FR1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="FS1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="FT1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="FU1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="FV1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="FW1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="FX1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="FY1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="FZ1" s="2" t="inlineStr">
+        <is>
+          <t>金蝶云</t>
+        </is>
+      </c>
+      <c r="GA1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="GB1" s="2" t="inlineStr">
+        <is>
+          <t>全链路固定库销</t>
+        </is>
+      </c>
+      <c r="GC1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="GD1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="GE1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量0413</t>
+        </is>
+      </c>
+      <c r="GF1" s="2" t="inlineStr">
+        <is>
+          <t>供应商预需求剩余数量</t>
+        </is>
+      </c>
+      <c r="GG1" s="2" t="inlineStr">
+        <is>
+          <t>最终需备货数量 0413</t>
+        </is>
+      </c>
+      <c r="GH1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0413</t>
+        </is>
+      </c>
+      <c r="GI1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回</t>
+        </is>
+      </c>
+      <c r="GJ1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="GK1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="GL1" s="2" t="inlineStr">
+        <is>
+          <t>旺季备货加权月均</t>
+        </is>
+      </c>
+      <c r="GM1" s="2" t="inlineStr">
+        <is>
+          <t>旺季1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="GN1" s="2" t="inlineStr">
+        <is>
+          <t>淡季备货加权月均</t>
+        </is>
+      </c>
+      <c r="GO1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="GP1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="GQ1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="GR1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="GS1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="GT1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="GU1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="GV1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="GW1" s="2" t="inlineStr">
+        <is>
+          <t>金蝶云</t>
+        </is>
+      </c>
+      <c r="GX1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="GY1" s="2" t="inlineStr">
+        <is>
+          <t>全链路固定库销</t>
+        </is>
+      </c>
+      <c r="GZ1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="HA1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="HB1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量0413</t>
+        </is>
+      </c>
+      <c r="HC1" s="2" t="inlineStr">
+        <is>
+          <t>供应商预需求剩余数量</t>
+        </is>
+      </c>
+      <c r="HD1" s="2" t="inlineStr">
+        <is>
+          <t>最终需备货数量 0413</t>
+        </is>
+      </c>
+      <c r="HE1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0413</t>
+        </is>
+      </c>
+      <c r="HF1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回</t>
+        </is>
+      </c>
+      <c r="HG1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="HH1" s="2" t="inlineStr">
+        <is>
+          <t>近30天销量</t>
+        </is>
+      </c>
+      <c r="HI1" s="2" t="inlineStr">
+        <is>
+          <t>旺季备货加权月均</t>
+        </is>
+      </c>
+      <c r="HJ1" s="2" t="inlineStr">
+        <is>
+          <t>旺季1.1倍系数月销</t>
+        </is>
+      </c>
+      <c r="HK1" s="2" t="inlineStr">
+        <is>
+          <t>淡季备货加权月均</t>
+        </is>
+      </c>
+      <c r="HL1" s="2" t="inlineStr">
+        <is>
+          <t>FBA可用</t>
+        </is>
+      </c>
+      <c r="HM1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="HN1" s="2" t="inlineStr">
+        <is>
+          <t>PO可用</t>
+        </is>
+      </c>
+      <c r="HO1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途</t>
+        </is>
+      </c>
+      <c r="HP1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓可用</t>
+        </is>
+      </c>
+      <c r="HQ1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+      <c r="HR1" s="2" t="inlineStr">
+        <is>
+          <t>本地可用</t>
+        </is>
+      </c>
+      <c r="HS1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途</t>
+        </is>
+      </c>
+      <c r="HT1" s="2" t="inlineStr">
+        <is>
+          <t>金蝶云</t>
+        </is>
+      </c>
+      <c r="HU1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库存</t>
+        </is>
+      </c>
+      <c r="HV1" s="2" t="inlineStr">
+        <is>
+          <t>全链路固定库销</t>
+        </is>
+      </c>
+      <c r="HW1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（近30天销量）</t>
+        </is>
+      </c>
+      <c r="HX1" s="2" t="inlineStr">
+        <is>
+          <t>全链路库销比（加权月均）</t>
+        </is>
+      </c>
+      <c r="HY1" s="2" t="inlineStr">
+        <is>
+          <t>需备货数量0518</t>
+        </is>
+      </c>
+      <c r="HZ1" s="2" t="inlineStr">
+        <is>
+          <t>供应商预需求剩余数量</t>
+        </is>
+      </c>
+      <c r="IA1" s="2" t="inlineStr">
+        <is>
+          <t>最终需备货数量 0518</t>
+        </is>
+      </c>
+      <c r="IB1" s="2" t="inlineStr">
+        <is>
+          <t>运营最终确认 0518</t>
+        </is>
+      </c>
+      <c r="IC1" s="2" t="inlineStr">
+        <is>
+          <t>最终备货数量-计划返回</t>
+        </is>
+      </c>
+      <c r="ID1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>平台销售编码</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>VC近7天销量</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>VC近14天销量</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>VC近30天销量</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>VC近30天销售额$</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>VC日均销量</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>PO在库</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>PO在库金额$</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>库龄超90天PO库存数</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>库龄超90天PO库存金额</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>PO库销比</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途_OMS</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PO在途_VC后台</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>SC近7天销量</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>SC近14天销量</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>SC近30天销量</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>SC日均销量</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在库</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>FBA库销比</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>FBA在途</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在库</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>VC-PO近30天销量</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>VC-PO近30天销售额$</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓库销比</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>海外仓在途</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>仓库名称</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>仓库类型</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>站点</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>品线</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>业务分类</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>系列</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>商品状态</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>平台SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>仓库类型</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>181-270</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>271-365</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>365天以上</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>30天出库</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1341EAF139XUS</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="n">
-        <v>100</v>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>产品编码</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>尾程类型</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>可用库存</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>可售库存</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>不可售库存</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>待上架库存</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>头程在途</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>采购在途（剩余订单）</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>总库存数量</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>总库存金额</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>采购单价</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>品牌名称</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>产品分类</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>是否VC锁定</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>仓库所在国家</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>开发人员</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>单箱数量</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/库存看板数据-模板.xlsx
+++ b/库存看板数据-模板.xlsx
@@ -443,7 +443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>库存看板数据模板 v4 · 使用说明</t>
+          <t>库存看板数据模板 v5 · 使用说明</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>共5个子表，表头与系统下载表完全一致。下载时按部门统一筛选口径：</t>
+          <t>共5个子表，表头与系统下载表完全一致。下载筛选口径：</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>筛选：近30天。每人只有自己权限 → 把自己的数据粘贴到【自己名字】下方分块（保留运营列名字）</t>
+          <t>筛选：近30天。组长下载所有人的数据粘贴（数据带运营列则自动识别归属）</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>粘贴方式：下载表格【删掉表头行】→ 数据粘贴到对应子表（数据从第2行开始）</t>
+          <t>粘贴：下载表格【删掉表头行】→ 数据粘贴到对应子表（数据从第2行开始）</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS20"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,11 +1088,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>向海</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -1138,888 +1134,6 @@
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>张紫莹</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>戴杨芳</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>尹芳</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>雷冰洁</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>陈景</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>方静敏</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>苏雨晴</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PHILTOP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>↑ 每个运营把自己的近30天数据粘贴到自己名字下方（不要覆盖运营列名字）</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/库存看板数据-模板.xlsx
+++ b/库存看板数据-模板.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VC库存销售汇总" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库存明细报表" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库龄报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IFS待发货" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +34,10 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,7 +72,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -443,7 +448,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>库存看板数据模板 v5 · 使用说明</t>
+          <t>库存看板数据模板 v6 · 使用说明</t>
         </is>
       </c>
     </row>
@@ -459,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>共5个子表，表头与系统下载表完全一致。下载筛选口径：</t>
+          <t>共6个子表，表头与系统下载表完全一致。下载筛选口径：</t>
         </is>
       </c>
     </row>
@@ -471,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器</t>
+          <t>筛选：业务分类=滤清器（只用于抓取【入库数量】等BI抓不到的数据）</t>
         </is>
       </c>
     </row>
@@ -483,7 +488,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>筛选：近30天。组长下载所有人的数据粘贴（数据带运营列则自动识别归属）</t>
+          <t>筛选：近30天。用于抓取【近30天销量】（日/周/月维度均可，自动聚合）。组长下载全员数据粘贴</t>
         </is>
       </c>
     </row>
@@ -495,7 +500,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器</t>
+          <t>筛选：业务分类=滤清器。用于抓取【PO在库/PO在途/PO销量/库龄超90天】</t>
         </is>
       </c>
     </row>
@@ -507,7 +512,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器</t>
+          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器（补充采购在途等）</t>
         </is>
       </c>
     </row>
@@ -519,77 +524,182 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器</t>
+          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器（抓取库龄分档）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  IFS待发货</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>抓取【IFS待发货】数量（如无权限可留空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>粘贴：下载表格【删掉表头行】→ 数据粘贴到对应子表（数据从第2行开始）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>没填的子表留空：留空字段自动用 BI/ERP 实时数据；填了的字段以你填的为准</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>数据优先级：BI/ERP 实时数据（FBA/海外仓/本地库存）默认保留实时值；</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BI 抓不到的（PO、销量、IFS、库龄、入库、采购在途）从模板对应子表抓取</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>常见问题</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>粘贴：下载表格【删掉表头行】→ 数据粘贴到对应子表（数据从第2行开始）。没填的子表留空即可</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Q: 粘贴后表头还在</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>A: 上传自动识别表头行跳过</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q: 列顺序不一致</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A: 按列名识别，顺序可不同</t>
-        </is>
-      </c>
+          <t>【BI抓不到、从模板导入的数据】</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">  PO在库/PO在途/PO近30天销量/库龄超90天PO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>← VC库存销售汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  近30天销量（出库销量聚合）</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>← 运营综合分析明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  IFS待发货</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>← IFS待发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  库龄分档（0-30/31-60/.../365+天）</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>← 库龄报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  入库数量（近7/14/30天）</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>← 进销存报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  采购在途</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>← 进销存报表/库存明细（BI接口为0时覆盖）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>常见问题</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q: 粘贴后表头还在</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A: 上传自动识别表头行跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q: 列顺序不一致</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A: 按列名识别，顺序可不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Q: 只填了1个子表</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>A: 可以，其余自动用实时数据</t>
         </is>
@@ -1620,4 +1730,40 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>IFS待发货（占位表头，收到真实IFS表后更新）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>IFS待发货数量</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/库存看板数据-模板.xlsx
+++ b/库存看板数据-模板.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,10 +34,6 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
     </font>
     <font>
       <b val="1"/>
@@ -72,7 +68,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -147,6 +143,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3619500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3619500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -438,11 +489,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +527,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器（只用于抓取【入库数量】等BI抓不到的数据）</t>
+          <t>筛选：业务分类=滤清器</t>
         </is>
       </c>
     </row>
@@ -488,7 +539,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>筛选：近30天。用于抓取【近30天销量】（日/周/月维度均可，自动聚合）。组长下载全员数据粘贴</t>
+          <t>筛选：近30天。组长下载所有人的数据粘贴（带运营列自动识别归属）</t>
         </is>
       </c>
     </row>
@@ -500,7 +551,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器。用于抓取【PO在库/PO在途/PO销量/库龄超90天】</t>
+          <t>筛选：业务分类=滤清器</t>
         </is>
       </c>
     </row>
@@ -512,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器（补充采购在途等）</t>
+          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器</t>
         </is>
       </c>
     </row>
@@ -524,7 +575,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器（抓取库龄分档）</t>
+          <t>筛选：业务分类=滤清器,空气滤清器,空调滤清器,组合滤清器</t>
         </is>
       </c>
     </row>
@@ -536,40 +587,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>抓取【IFS待发货】数量（如无权限可留空）</t>
+          <t>IFS系统导出「发货需求」（下载方法见下方截图教程）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>粘贴：下载表格【删掉表头行】→ 数据粘贴到对应子表（数据从第2行开始）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>数据优先级：BI/ERP 实时数据（FBA/海外仓/本地库存）默认保留实时值；</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BI 抓不到的（PO、销量、IFS、库龄、入库、采购在途）从模板对应子表抓取</t>
+          <t>导入优先级：BI/ERP 实时数据保留（FBA/海外仓/本地库存）；BI 抓不到的（PO、销量、库龄、IFS、入库）从模板抓取</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>粘贴：下载表格【删掉表头行】→ 数据粘贴到对应子表（数据从第2行开始）。没填的子表留空即可</t>
+          <t>没填的子表留空：留空字段自动用 BI/ERP 实时数据；填了的字段以你填的为准</t>
         </is>
       </c>
     </row>
@@ -580,7 +634,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【BI抓不到、从模板导入的数据】</t>
+          <t>📥 IFS待发货 · 下载教程（如下截图）</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -588,125 +642,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PO在库/PO在途/PO近30天销量/库龄超90天PO</t>
+          <t>步骤1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>← VC库存销售汇总</t>
+          <t>系统 → 待发货需求查询 → 筛选：状态=待发货、日期选近30天</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  近30天销量（出库销量聚合）</t>
+          <t>步骤2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>← 运营综合分析明细</t>
+          <t>勾选需要的记录 → 导出 Excel（表头保留）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IFS待发货</t>
+          <t>步骤3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>← IFS待发货</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  库龄分档（0-30/31-60/.../365+天）</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>← 库龄报表</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  入库数量（近7/14/30天）</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>← 进销存报表</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  采购在途</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>← 进销存报表/库存明细（BI接口为0时覆盖）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>常见问题</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q: 粘贴后表头还在</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>A: 上传自动识别表头行跳过</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Q: 列顺序不一致</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>A: 按列名识别，顺序可不同</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Q: 只填了1个子表</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>A: 可以，其余自动用实时数据</t>
+          <t>把导出的表格删掉表头行，粘贴到「IFS待发货」子表</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -967,7 +938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS2"/>
+  <dimension ref="A1:AS1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1196,53 +1167,6 @@
           <t>返利率</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1738,28 +1662,328 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>IFS待发货（占位表头，收到真实IFS表后更新）</t>
+          <t>发货单号</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>发运单号</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>NS发运单号</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>NS调拨计划ID</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>预装柜号</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>发货仓</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>收货仓</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>发货方式</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>站点</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>运营</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>PMC</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>发货时间</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>实际出库时间</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>平台商品编码</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>IFS待发货数量</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>FNSKU</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>发货数量</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>发运数量</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>货件编码</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>FBA/FBT仓库代码</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>是否锁仓</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>供应商名称</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>NS同步时间</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>彩箱标</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>外箱标</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>下单主体公司</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>品线</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>产品分类</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>单据类型</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>预计发货数量</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>是否仓库装箱</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>预测销量</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>追踪号</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>每箱数量</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>总箱数</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>长</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>宽</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>毛重(kg)</t>
+        </is>
+      </c>
+      <c r="AU1" s="2" t="inlineStr">
+        <is>
+          <t>总重(kg)</t>
+        </is>
+      </c>
+      <c r="AV1" s="2" t="inlineStr">
+        <is>
+          <t>单体积(m³)</t>
+        </is>
+      </c>
+      <c r="AW1" s="2" t="inlineStr">
+        <is>
+          <t>总体积(m³)</t>
+        </is>
+      </c>
+      <c r="AX1" s="2" t="inlineStr">
+        <is>
+          <t>原发货需求</t>
+        </is>
+      </c>
+      <c r="AY1" s="2" t="inlineStr">
+        <is>
+          <t>新发货需求</t>
+        </is>
+      </c>
+      <c r="AZ1" s="2" t="inlineStr">
+        <is>
+          <t>实际到货时间</t>
+        </is>
+      </c>
+      <c r="BA1" s="2" t="inlineStr">
+        <is>
+          <t>物流属性</t>
+        </is>
+      </c>
+      <c r="BB1" s="2" t="inlineStr">
+        <is>
+          <t>货件类型</t>
+        </is>
+      </c>
+      <c r="BC1" s="2" t="inlineStr">
+        <is>
+          <t>入库配置费</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>新区域</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>子提单号</t>
+        </is>
+      </c>
+      <c r="BF1" s="2" t="inlineStr">
+        <is>
+          <t>货件批次号</t>
+        </is>
+      </c>
+      <c r="BG1" s="2" t="inlineStr">
+        <is>
+          <t>省/州</t>
+        </is>
+      </c>
+      <c r="BH1" s="2" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="BI1" s="2" t="inlineStr">
+        <is>
+          <t>地址</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>邮编</t>
+        </is>
+      </c>
+      <c r="BK1" s="2" t="inlineStr">
+        <is>
+          <t>是否整箱上架</t>
+        </is>
+      </c>
+      <c r="BL1" s="2" t="inlineStr">
+        <is>
+          <t>箱规异常信息</t>
         </is>
       </c>
     </row>

--- a/库存看板数据-模板.xlsx
+++ b/库存看板数据-模板.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IFS待发货" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营综合分析明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进销存报表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IFS待发货" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营综合分析明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -429,7 +430,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>滤清备货库存看板 · 数据模板 v7（精简版）</t>
+          <t>滤清备货库存看板 · 数据模板 v7.1</t>
         </is>
       </c>
     </row>
@@ -470,90 +471,69 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. IFS待发货：IFS 系统导出的「发货需求」表（发货单号/商品编码/发货数量等，64列真实表头）</t>
+          <t>1. IFS待发货：IFS 系统导出的「发货需求」表（64列真实表头）→ 按商品编码聚合待发货数量（ifs_pending）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → 看板自动按商品编码聚合出每个SKU的待发货数量（ifs_pending），用于0库存到货统计</t>
+          <t>2. 运营综合分析明细：运营综合导出（含 ASIN/sku/日期/出库销量，近30天日维度）→ 销量按 ASIN/sku 自动归属运营</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. 运营综合分析明细：运营综合导出（含 平台销售编码=ASIN、sku、日期、出库销量，近30天日维度）</t>
+          <t>3. 进销存报表：进销存导出的库存报表（含采购在途库存列）→ 补采购在途（BI/ERP 接口无此数据，必须靠此表）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → 看板按 ASIN/sku 自动匹配到对应商品，销量自动归属到映射表中的运营</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → 谁导出的表不重要：所有运营的表都能导入，看板自动识别归属（ASIN-运营映射表在板块1下方）</t>
+          <t>【数据来源分工】</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>· BI/ERP 接口实时抓：FBA可用/在途、海外仓可用/在途、本地、PO在库/在途（MCP已更新）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【当前仅你（向海）有导出权限】</t>
+          <t>· 模板导入弥补 BI 抓不到的：IFS待发货、近30天销量、采购在途</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>· 先导你自己的近30天销量表即可，逻辑已按全量设计</t>
+          <t>· 销量自动归属：谁导的表都能导入，看板按 ASIN-运营映射表（板块1下方）自动识别运营</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>· 拿到其他运营的表后，直接继续导入（可多运营表多次导入，自动覆盖更新）</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【当前仅向海有销量导出权限】</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【其他数据来源】</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>· 库存（FBA/PO/海外仓/本地/采购在途）、库龄：BI/ERP 接口实时抓取（MCP已更新）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>· PO在库/PO在途/PO在途OMS/库龄7层：BI 已提供字段</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>· IFS待发货、近30天销量：BI 暂无接口 → 用本模板导入弥补</t>
+          <t>· 先导自己的近30天销量表即可，逻辑已按全量设计；拿到其他运营的表继续导入即可</t>
         </is>
       </c>
     </row>
@@ -568,328 +548,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>发货单号</t>
+          <t>商品编码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>发运单号</t>
+          <t>品线</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>NS发运单号</t>
+          <t>业务分类</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NS调拨计划ID</t>
+          <t>系列</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>预装柜号</t>
+          <t>型号</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>发货仓</t>
+          <t>商品等级</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>收货仓</t>
+          <t>开发人员</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>发货方式</t>
+          <t>FBA可用库存</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>FBA在途库存</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>店铺</t>
+          <t>海外仓可用库存</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>站点</t>
+          <t>海外仓在途库存</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>运营</t>
+          <t>本地仓可用库存</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>PMC</t>
+          <t>总库存</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>发货时间</t>
+          <t>采购在途库存</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>实际出库时间</t>
+          <t>含采购在途总库存</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>商品编码</t>
+          <t>总库存金额</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>平台商品编码</t>
+          <t>含采购在途总库存金额</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ASIN</t>
+          <t>7天销量</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>FNSKU</t>
+          <t>14天销量</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>发货数量</t>
+          <t>30天销量</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>发运数量</t>
+          <t>30-60天销量</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>货件编码</t>
+          <t>60-90天销量</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>FBA/FBT仓库代码</t>
+          <t>近7天入库数量</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>是否锁仓</t>
+          <t>近14天入库数量</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>供应商名称</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>NS同步时间</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>彩箱标</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>外箱标</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>下单主体公司</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>品线</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>产品分类</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>渠道</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>单据类型</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>预计发货数量</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>是否仓库装箱</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>预测销量</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>追踪号</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>每箱数量</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>总箱数</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>长</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>宽</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>毛重(kg)</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>总重(kg)</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>单体积(m³)</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>总体积(m³)</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>原发货需求</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>新发货需求</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>实际到货时间</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>物流属性</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>货件类型</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>入库配置费</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>新区域</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>子提单号</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>货件批次号</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>省/州</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>地址</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>邮编</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>是否整箱上架</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>箱规异常信息</t>
+          <t>近30天入库数量</t>
         </is>
       </c>
     </row>
@@ -904,6 +689,342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:BL1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>发货单号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>发运单号</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>NS发运单号</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>NS调拨计划ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>预装柜号</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>发货仓</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>收货仓</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>发货方式</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>站点</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>运营</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PMC</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>发货时间</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>实际出库时间</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>平台商品编码</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>FNSKU</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>发货数量</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>发运数量</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>货件编码</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>FBA/FBT仓库代码</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>是否锁仓</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>供应商名称</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>NS同步时间</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>彩箱标</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>外箱标</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>下单主体公司</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>品线</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>产品分类</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>单据类型</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>预计发货数量</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>是否仓库装箱</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>预测销量</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>追踪号</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>每箱数量</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>总箱数</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>长</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>宽</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>毛重(kg)</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>总重(kg)</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>单体积(m³)</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>总体积(m³)</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>原发货需求</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>新发货需求</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>实际到货时间</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>物流属性</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>货件类型</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>入库配置费</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>新区域</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>子提单号</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>货件批次号</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>省/州</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>地址</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>邮编</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>是否整箱上架</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>箱规异常信息</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/库存看板数据-模板.xlsx
+++ b/库存看板数据-模板.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进销存报表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库存明细报表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IFS待发货" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营综合分析明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进销存报表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -430,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>滤清备货库存看板 · 数据模板 v7.1</t>
+          <t>滤清备货库存看板 · 数据模板 v7.2</t>
         </is>
       </c>
     </row>
@@ -471,69 +472,66 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. IFS待发货：IFS 系统导出的「发货需求」表（64列真实表头）→ 按商品编码聚合待发货数量（ifs_pending）</t>
+          <t>1. 库存明细报表：BI 导出的库存明细（30列，含「采购在途（剩余订单）」列）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2. 运营综合分析明细：运营综合导出（含 ASIN/sku/日期/出库销量，近30天日维度）→ 销量按 ASIN/sku 自动归属运营</t>
+          <t xml:space="preserve">   → 采购在途 = 自营仓(本地仓)的采购在途（剩余订单），按商品编码聚合</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3. 进销存报表：进销存导出的库存报表（含采购在途库存列）→ 补采购在途（BI/ERP 接口无此数据，必须靠此表）</t>
+          <t>2. IFS待发货：IFS 系统「发货需求」表（64列）→ 按商品编码聚合待发货数量</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. 运营综合分析明细：运营综合导出（ASIN/sku/日期/出库销量）→ 销量自动归属运营</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【数据来源分工】</t>
+          <t>4. 进销存报表：进销存导出（25列）→ 补参考数据（采购在途备用）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>· BI/ERP 接口实时抓：FBA可用/在途、海外仓可用/在途、本地、PO在库/在途（MCP已更新）</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>· 模板导入弥补 BI 抓不到的：IFS待发货、近30天销量、采购在途</t>
+          <t>【数据来源分工】</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>· 销量自动归属：谁导的表都能导入，看板按 ASIN-运营映射表（板块1下方）自动识别运营</t>
+          <t>· BI/ERP 接口实时抓：FBA可用/在途、海外仓可用/在途、本地、PO在库/在途（MCP已更新）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>· 模板导入弥补：IFS待发货、近30天销量、采购在途（剩余订单，自营仓）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【当前仅向海有销量导出权限】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>· 先导自己的近30天销量表即可，逻辑已按全量设计；拿到其他运营的表继续导入即可</t>
+          <t>· 销量自动归属：谁导的表都能导入，按 ASIN-运营映射表自动识别运营</t>
         </is>
       </c>
     </row>
@@ -548,133 +546,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>商品编码</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>仓库名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>仓库类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>站点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>品线</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>业务分类</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>系列</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>型号</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>商品等级</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>商品状态</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>平台SKU</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>产品编码</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>尾程类型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>可用库存</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>可售库存</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>不可售库存</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>待上架库存</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>头程在途</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>采购在途（剩余订单）</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>总库存数量</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>总库存金额</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>采购单价</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>品牌名称</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>产品分类</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>是否VC锁定</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>仓库所在国家</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>开发人员</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FBA可用库存</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>FBA在途库存</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>海外仓可用库存</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>海外仓在途库存</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>本地仓可用库存</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>总库存</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>采购在途库存</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>含采购在途总库存</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>总库存金额</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>含采购在途总库存金额</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>7天销量</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>14天销量</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>30天销量</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>30-60天销量</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>60-90天销量</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>近7天入库数量</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>近14天入库数量</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>近30天入库数量</t>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>单箱数量</t>
         </is>
       </c>
     </row>
@@ -1253,4 +1276,145 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>品线</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>业务分类</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>系列</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>商品等级</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>开发人员</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>FBA可用库存</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>FBA在途库存</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>海外仓可用库存</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>海外仓在途库存</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>本地仓可用库存</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>总库存</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>采购在途库存</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>含采购在途总库存</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>总库存金额</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>含采购在途总库存金额</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>7天销量</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>14天销量</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>30天销量</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>30-60天销量</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>60-90天销量</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>近7天入库数量</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>近14天入库数量</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>近30天入库数量</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>